--- a/db/site_db_history.xlsx
+++ b/db/site_db_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="歷史" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'歷史'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'歷史'!$A$1:$K$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -543,8 +543,51 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-15 19:31</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>46</v>
+      </c>
+      <c r="D3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>34</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>海運</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>E-mini Nasdaq-100</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/db/site_db_history.xlsx
+++ b/db/site_db_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="歷史" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'歷史'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'歷史'!$A$1:$K$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -586,8 +586,51 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-10-20 19:31</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>59</v>
+      </c>
+      <c r="D4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>34</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>油氣開採</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>E-mini Nasdaq-100</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/db/site_db_history.xlsx
+++ b/db/site_db_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="歷史" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'歷史'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'歷史'!$A$1:$K$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -629,8 +629,51 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-22 19:31</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>42</v>
+      </c>
+      <c r="D5" t="n">
+        <v>60</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>34</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>油氣開採</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>E-mini Nasdaq-100</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:K5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/db/site_db_history.xlsx
+++ b/db/site_db_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="歷史" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'歷史'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'歷史'!$A$1:$K$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -672,8 +672,51 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-10-24 19:32</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>油氣開採</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>10 年美債</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K5"/>
+  <autoFilter ref="A1:K6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/db/site_db_history.xlsx
+++ b/db/site_db_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="歷史" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'歷史'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'歷史'!$A$1:$K$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -715,8 +715,51 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-10-28 19:30</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>43</v>
+      </c>
+      <c r="D7" t="n">
+        <v>60</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>34</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>網絡安全</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>10 年美債</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K6"/>
+  <autoFilter ref="A1:K7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/db/site_db_history.xlsx
+++ b/db/site_db_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="歷史" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'歷史'!$A$1:$K$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'歷史'!$A$1:$K$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -758,8 +758,51 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:30</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>35</v>
+      </c>
+      <c r="D8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>34</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>網絡安全</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>10 年美債</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K7"/>
+  <autoFilter ref="A1:K8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/db/site_db_history.xlsx
+++ b/db/site_db_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="歷史" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'歷史'!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'歷史'!$A$1:$K$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -801,8 +801,51 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-30 19:30</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>41</v>
+      </c>
+      <c r="D9" t="n">
+        <v>60</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>34</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>海運</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>10 年美債</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K8"/>
+  <autoFilter ref="A1:K9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/db/site_db_history.xlsx
+++ b/db/site_db_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="歷史" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'歷史'!$A$1:$K$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'歷史'!$A$1:$K$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -844,8 +844,51 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-11-01 00:03</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>52</v>
+      </c>
+      <c r="D10" t="n">
+        <v>60</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>34</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>油氣開採</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>E-mini Nasdaq-100</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K9"/>
+  <autoFilter ref="A1:K10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>